--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230901_20240301.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230901_20240301.xlsx
@@ -1141,37 +1141,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.16260162601627</v>
+        <v>56.91056910569105</v>
       </c>
       <c r="C17" t="n">
-        <v>39.83739837398374</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="D17" t="n">
-        <v>64.20785981673261</v>
+        <v>90.56368281312801</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>INE298A01020</t>
+          <t>INE274J01014</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>-20.32520325203253</v>
+        <v>-15.44715447154471</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I17" t="n">
         <v>84</v>
       </c>
       <c r="J17" t="n">
-        <v>2738.65</v>
+        <v>364.35</v>
       </c>
       <c r="K17" t="n">
         <v>16</v>
@@ -1229,37 +1229,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56.91056910569105</v>
+        <v>60.16260162601627</v>
       </c>
       <c r="C19" t="n">
-        <v>41.46341463414634</v>
+        <v>39.83739837398374</v>
       </c>
       <c r="D19" t="n">
-        <v>90.56368281312801</v>
+        <v>64.20785981673261</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>INE274J01014</t>
+          <t>INE298A01020</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>-15.44715447154471</v>
+        <v>-20.32520325203253</v>
       </c>
       <c r="H19" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
         <v>84</v>
       </c>
       <c r="J19" t="n">
-        <v>364.35</v>
+        <v>2738.65</v>
       </c>
       <c r="K19" t="n">
         <v>18</v>
